--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/create-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/create-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
-  <si>
-    <t>Statement: ExerciseRepository.create(data) – creates a new exercise. Names must be unique.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+  <si>
+    <t>Statement: ExerciseRepository.create(data) – Creates a new exercise record. Returns the created Exercise on success. Throws ConflictError if an exercise with the same name already exists.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateExerciseInput { name, description?, muscleGroup, equipmentNeeded }</t>
+    <t>Input: data: CreateExerciseInput { name: string, ... }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. An exercise with the given name may or may not already exist.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;Exercise&gt; | throws ConflictError</t>
+    <t>Output: Promise&lt;Exercise&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Persists row or throws ConflictError.</t>
+    <t>On success: Exercise returned with result matching expectedReturn and result.name matching input name. On failure: ConflictError thrown with message "Exercise name already in use".</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,10 +67,10 @@
     <t>Name uniqueness</t>
   </si>
   <si>
-    <t>Name not in catalogue</t>
-  </si>
-  <si>
-    <t>Name exists (ConflictError)</t>
+    <t>Name not yet registered → Exercise returned with result.name: VALID_CREATE_INPUT.name</t>
+  </si>
+  <si>
+    <t>Name already registered → ConflictError("Exercise name already in use")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -91,10 +91,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Unique name</t>
-  </si>
-  <si>
-    <t>Returns Exercise</t>
+    <t>data: VALID_CREATE_INPUT (name not found in DB)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result equal to MOCK_EXERCISE and result.name: VALID_CREATE_INPUT.name</t>
   </si>
   <si>
     <t>Passed</t>
@@ -103,10 +103,10 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Duplicate name</t>
-  </si>
-  <si>
-    <t>Throws ConflictError</t>
+    <t>data: VALID_CREATE_INPUT (name already in DB)</t>
+  </si>
+  <si>
+    <t>throws ConflictError("Exercise name already in use")</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -124,12 +124,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Unique exercise name</t>
-  </si>
-  <si>
-    <t>Duplicate exercise name</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -160,7 +154,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-01</t>
+    <t>REPO-13</t>
   </si>
   <si>
     <t>n/a</t>
@@ -726,7 +720,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -916,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>25</v>
@@ -936,7 +930,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -970,16 +964,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -987,39 +981,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1034,19 +1028,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
